--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_ending4(1).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_ending4(1).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="21105" windowHeight="10125"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_结局4（上）" sheetId="1" r:id="rId1"/>
@@ -660,7 +660,25 @@
     <t>他用眼角的余光瞄了瞄身后一动不动的克拉克，眼神轻蔑而戏谑。</t>
   </si>
   <si>
-    <t>loadScript(结局4（下）_1, 1)</t>
+    <r>
+      <t>loadScript(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sntzm_ending4(2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>, 1)</t>
+    </r>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=59; gotomainline=结局4（下）_1</t>
@@ -1853,7 +1871,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1861,6 +1879,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4720,7 +4741,7 @@
       <c r="J61" t="s">
         <v>15</v>
       </c>
-      <c r="K61" t="s">
+      <c r="K61" s="3" t="s">
         <v>208</v>
       </c>
       <c r="L61" t="s">
